--- a/output/2026-09-06_09_Slovenia_Posavska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_09_Slovenia_Posavska_Depolverazione_Trattamento_aria.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Filiale confermata via najdi.si/bizi.si; catalogo online inpos.eu conferma vendita di aspiratori industriali (sesalniki industrijski).</t>
+          <t>Filiale confermata via najdi.si/bizi.si; catalogo online inpos.eu conferma vendita di aspiratori industriali (sesalniki industrijski). [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Filiale distinta da INPOS Krško (area geografica diversa, non duplicato); dati confermati via ricerca.</t>
+          <t>Filiale distinta da INPOS Krško (area geografica diversa, non duplicato); dati confermati via ricerca. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Email non presente nella lista grezza originale, trovata e verificata tramite ricerca; catena confermata, vendita industrijski sesalniki confermata dal sito (Metabo, Kärcher, Bosch Professional, Einhell).</t>
+          <t>Email non presente nella lista grezza originale, trovata e verificata tramite ricerca; catena confermata, vendita industrijski sesalniki confermata dal sito (Metabo, Kärcher, Bosch Professional, Einhell). [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
